--- a/cp-ins-iti-105/ig/StructureDefinition-pdsm-comprehensive-document-reference.xlsx
+++ b/cp-ins-iti-105/ig/StructureDefinition-pdsm-comprehensive-document-reference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T16:40:58+00:00</t>
+    <t>2026-07-29T17:09:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/cp-ins-iti-105/ig/StructureDefinition-pdsm-comprehensive-document-reference.xlsx
+++ b/cp-ins-iti-105/ig/StructureDefinition-pdsm-comprehensive-document-reference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T17:09:31+00:00</t>
+    <t>2026-07-30T07:55:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/cp-ins-iti-105/ig/StructureDefinition-pdsm-comprehensive-document-reference.xlsx
+++ b/cp-ins-iti-105/ig/StructureDefinition-pdsm-comprehensive-document-reference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T07:55:20+00:00</t>
+    <t>2026-07-30T08:19:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/cp-ins-iti-105/ig/StructureDefinition-pdsm-comprehensive-document-reference.xlsx
+++ b/cp-ins-iti-105/ig/StructureDefinition-pdsm-comprehensive-document-reference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T08:19:35+00:00</t>
+    <t>2026-07-30T08:31:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/cp-ins-iti-105/ig/StructureDefinition-pdsm-comprehensive-document-reference.xlsx
+++ b/cp-ins-iti-105/ig/StructureDefinition-pdsm-comprehensive-document-reference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T08:31:43+00:00</t>
+    <t>2026-07-30T10:07:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/cp-ins-iti-105/ig/StructureDefinition-pdsm-comprehensive-document-reference.xlsx
+++ b/cp-ins-iti-105/ig/StructureDefinition-pdsm-comprehensive-document-reference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T10:07:17+00:00</t>
+    <t>2026-07-30T12:04:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
